--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/11,08,26 Останкино СЫРЫ/дв 11,08,26 млрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/11,08,26 Останкино СЫРЫ/дв 11,08,26 млрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\11,08,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F89F23-0DC2-42D5-9B20-0D2FABF09475}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AD9747-7DBF-4264-AC12-B9B2715F76F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
